--- a/2025-T3/T3B1-ICTPMG613-Manage_ICT_project_plan/2-ICTPMG613-Task2/ICTPMG613_AssessmentTask_Manuel_S_Perez_E-Pert_Chart.xlsx
+++ b/2025-T3/T3B1-ICTPMG613-Manage_ICT_project_plan/2-ICTPMG613-Task2/ICTPMG613_AssessmentTask_Manuel_S_Perez_E-Pert_Chart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manue\Documents\Assessments\TERM3\T3B1-ICTPMG613-Manage_ICT_project_plan\2-ICTPMG613-Assessment_Task 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mannsee/Documents/Assessments/2025-T3/T3B1-ICTPMG613-Manage_ICT_project_plan/2-ICTPMG613-Task2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7965BE5B-9946-4D50-8C66-97F6E97534D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D016FD6-AF2F-B346-A3B4-93D4CBEF154D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2E7573F3-6188-4FA9-9041-50436B486355}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="23260" windowHeight="17660" activeTab="4" xr2:uid="{2E7573F3-6188-4FA9-9041-50436B486355}"/>
   </bookViews>
   <sheets>
     <sheet name="Chart" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="430">
   <si>
     <t>Activity</t>
   </si>
@@ -642,12 +641,6 @@
     <t>Step</t>
   </si>
   <si>
-    <t>Change proposed by the client</t>
-  </si>
-  <si>
-    <t>Change proposed by us</t>
-  </si>
-  <si>
     <t>Proccess</t>
   </si>
   <si>
@@ -1282,6 +1275,63 @@
   </si>
   <si>
     <t>Archive all project records and documentation for compliance and reference.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client Change Requests </t>
+  </si>
+  <si>
+    <t>Internal Change Requests</t>
+  </si>
+  <si>
+    <t>Budget Variance Threshold Control</t>
+  </si>
+  <si>
+    <t>Identify budget variance</t>
+  </si>
+  <si>
+    <t>The Project Manager will compare planned vs actual expenditure on a regular basis to detect any cost deviation.</t>
+  </si>
+  <si>
+    <t>Assess variance threshold</t>
+  </si>
+  <si>
+    <t>If project costs exceed 10% of the allocated budget for any component, a financial review will be triggered.</t>
+  </si>
+  <si>
+    <t>Analyse cause of variance</t>
+  </si>
+  <si>
+    <t>Project Manager, Project Team</t>
+  </si>
+  <si>
+    <t>The Project Manager will work with relevant team members to identify the cause of the budget overrun and assess its impact.</t>
+  </si>
+  <si>
+    <t>Recommend corrective action</t>
+  </si>
+  <si>
+    <t>The Project Manager will determine whether cost adjustments, scope refinement, or resource reallocation are required.</t>
+  </si>
+  <si>
+    <t>Seek approval</t>
+  </si>
+  <si>
+    <t>Project Sponsor / Steering Committee</t>
+  </si>
+  <si>
+    <t>Approval must be obtained before any additional expenditure is incurred.</t>
+  </si>
+  <si>
+    <t>Update budget baseline</t>
+  </si>
+  <si>
+    <t>If approved, the Project Manager will update budget documentation and communicate changes to stakeholders.</t>
+  </si>
+  <si>
+    <t>Monitor ongoing expenditure</t>
+  </si>
+  <si>
+    <t>Budget performance will continue to be monitored to ensure costs remain within acceptable limits.</t>
   </si>
 </sst>
 </file>
@@ -1875,19 +1925,19 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:H70"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="28.21875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="5" max="5" width="11.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="28.1640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1913,7 +1963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>4</v>
       </c>
@@ -1941,7 +1991,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A3" s="17" t="s">
         <v>5</v>
       </c>
@@ -1969,7 +2019,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A4" s="17" t="s">
         <v>6</v>
       </c>
@@ -1997,7 +2047,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
@@ -2025,7 +2075,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="17" t="s">
         <v>8</v>
       </c>
@@ -2053,7 +2103,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" s="17" t="s">
         <v>9</v>
       </c>
@@ -2081,7 +2131,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>10</v>
       </c>
@@ -2109,7 +2159,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
         <v>11</v>
       </c>
@@ -2137,7 +2187,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="69" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
         <v>12</v>
       </c>
@@ -2165,7 +2215,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="69" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
         <v>13</v>
       </c>
@@ -2193,7 +2243,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A12" s="17" t="s">
         <v>14</v>
       </c>
@@ -2221,7 +2271,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="69" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
         <v>15</v>
       </c>
@@ -2249,7 +2299,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
         <v>16</v>
       </c>
@@ -2277,7 +2327,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
         <v>18</v>
       </c>
@@ -2305,7 +2355,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
         <v>19</v>
       </c>
@@ -2333,7 +2383,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
         <v>116</v>
       </c>
@@ -2361,7 +2411,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
         <v>20</v>
       </c>
@@ -2389,7 +2439,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
         <v>21</v>
       </c>
@@ -2417,7 +2467,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A20" s="17" t="s">
         <v>22</v>
       </c>
@@ -2445,7 +2495,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
         <v>23</v>
       </c>
@@ -2473,7 +2523,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="17" t="s">
         <v>24</v>
       </c>
@@ -2501,7 +2551,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2529,7 +2579,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A24" s="17" t="s">
         <v>27</v>
       </c>
@@ -2557,7 +2607,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A25" s="17" t="s">
         <v>28</v>
       </c>
@@ -2585,7 +2635,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A26" s="17" t="s">
         <v>29</v>
       </c>
@@ -2613,7 +2663,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A27" s="17" t="s">
         <v>30</v>
       </c>
@@ -2641,7 +2691,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="75" x14ac:dyDescent="0.2">
       <c r="A28" s="17" t="s">
         <v>32</v>
       </c>
@@ -2669,7 +2719,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="69" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A29" s="17" t="s">
         <v>33</v>
       </c>
@@ -2697,7 +2747,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="69" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
         <v>34</v>
       </c>
@@ -2725,7 +2775,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="69" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A31" s="17" t="s">
         <v>35</v>
       </c>
@@ -2753,7 +2803,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A32" s="17" t="s">
         <v>36</v>
       </c>
@@ -2781,7 +2831,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A33" s="17" t="s">
         <v>37</v>
       </c>
@@ -2809,7 +2859,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A34" s="17" t="s">
         <v>38</v>
       </c>
@@ -2837,7 +2887,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A35" s="17" t="s">
         <v>39</v>
       </c>
@@ -2865,7 +2915,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A36" s="17" t="s">
         <v>40</v>
       </c>
@@ -2893,7 +2943,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="69" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A37" s="17" t="s">
         <v>42</v>
       </c>
@@ -2921,7 +2971,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A38" s="17" t="s">
         <v>43</v>
       </c>
@@ -2949,7 +2999,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A39" s="17" t="s">
         <v>117</v>
       </c>
@@ -2977,7 +3027,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A40" s="17" t="s">
         <v>45</v>
       </c>
@@ -3005,7 +3055,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="69" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="75" x14ac:dyDescent="0.2">
       <c r="A41" s="17" t="s">
         <v>46</v>
       </c>
@@ -3033,7 +3083,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A42" s="17" t="s">
         <v>118</v>
       </c>
@@ -3061,7 +3111,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="17" t="s">
         <v>48</v>
       </c>
@@ -3089,7 +3139,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A44" s="17" t="s">
         <v>49</v>
       </c>
@@ -3117,7 +3167,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A45" s="17" t="s">
         <v>122</v>
       </c>
@@ -3145,7 +3195,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A46" s="17" t="s">
         <v>50</v>
       </c>
@@ -3173,7 +3223,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A47" s="17" t="s">
         <v>51</v>
       </c>
@@ -3201,7 +3251,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" s="17" t="s">
         <v>52</v>
       </c>
@@ -3229,7 +3279,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A49" s="17" t="s">
         <v>54</v>
       </c>
@@ -3257,7 +3307,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="69" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A50" s="17" t="s">
         <v>56</v>
       </c>
@@ -3285,7 +3335,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A51" s="17" t="s">
         <v>57</v>
       </c>
@@ -3313,7 +3363,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A52" s="17" t="s">
         <v>59</v>
       </c>
@@ -3341,7 +3391,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A53" s="17" t="s">
         <v>60</v>
       </c>
@@ -3369,7 +3419,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A54" s="17" t="s">
         <v>61</v>
       </c>
@@ -3397,7 +3447,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="69" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A55" s="17" t="s">
         <v>62</v>
       </c>
@@ -3425,7 +3475,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A56" s="17" t="s">
         <v>63</v>
       </c>
@@ -3453,7 +3503,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A57" s="17" t="s">
         <v>64</v>
       </c>
@@ -3481,7 +3531,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A58" s="17" t="s">
         <v>65</v>
       </c>
@@ -3509,7 +3559,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A59" s="17" t="s">
         <v>66</v>
       </c>
@@ -3537,7 +3587,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A60" s="17" t="s">
         <v>67</v>
       </c>
@@ -3565,7 +3615,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A61" s="17" t="s">
         <v>68</v>
       </c>
@@ -3593,7 +3643,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A62" s="17" t="s">
         <v>69</v>
       </c>
@@ -3621,7 +3671,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A63" s="17" t="s">
         <v>70</v>
       </c>
@@ -3649,7 +3699,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A64" s="17" t="s">
         <v>71</v>
       </c>
@@ -3677,7 +3727,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
         <v>73</v>
       </c>
@@ -3705,7 +3755,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A66" s="17" t="s">
         <v>74</v>
       </c>
@@ -3733,7 +3783,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A67" s="17" t="s">
         <v>75</v>
       </c>
@@ -3761,7 +3811,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A68" s="17" t="s">
         <v>76</v>
       </c>
@@ -3789,7 +3839,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A69" s="17" t="s">
         <v>77</v>
       </c>
@@ -3817,7 +3867,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A70" s="17" t="s">
         <v>78</v>
       </c>
@@ -3854,15 +3904,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{081C22EC-4620-4117-A76D-1E4837839DB1}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" customWidth="1"/>
-    <col min="3" max="3" width="44.5546875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" customWidth="1"/>
+    <col min="3" max="3" width="44.5" style="4" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>170</v>
       </c>
@@ -3876,7 +3926,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="31" x14ac:dyDescent="0.2">
       <c r="A2" s="17">
         <v>1</v>
       </c>
@@ -3890,7 +3940,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="42" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="46" x14ac:dyDescent="0.2">
       <c r="A3" s="17">
         <f>A2+1</f>
         <v>2</v>
@@ -3905,7 +3955,7 @@
         <v>45877</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="17">
         <f t="shared" ref="A4:A13" si="0">A3+1</f>
         <v>3</v>
@@ -3920,7 +3970,7 @@
         <v>45877</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="17">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3935,7 +3985,7 @@
         <v>45881</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A6" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3950,7 +4000,7 @@
         <v>45889</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A7" s="17">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3965,7 +4015,7 @@
         <v>45889</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" s="17">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3980,7 +4030,7 @@
         <v>45897</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A9" s="17">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3995,7 +4045,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A10" s="17">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -4010,7 +4060,7 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A11" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -4025,7 +4075,7 @@
         <v>45898</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" s="17">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -4040,7 +4090,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" s="17">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -4064,66 +4114,66 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52962F3B-7E13-4F4A-95DB-0576158409CF}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="20.5546875" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="19.5" customWidth="1"/>
+    <col min="3" max="3" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="34" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="115.2" x14ac:dyDescent="0.3">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="112" x14ac:dyDescent="0.2">
       <c r="A2" s="35" t="s">
+        <v>300</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>301</v>
+      </c>
+      <c r="C2" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="B2" s="35" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+      <c r="A3" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="B3" s="35" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+      <c r="C3" s="35" t="s">
         <v>305</v>
       </c>
-      <c r="B3" s="35" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+      <c r="A4" s="35" t="s">
         <v>306</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="B4" s="35" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="C4" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="B4" s="35" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+      <c r="A5" s="35" t="s">
         <v>309</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="B5" s="35" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="s">
+      <c r="C5" s="35" t="s">
         <v>311</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>312</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -4134,14 +4184,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A6C9D0-B316-4A49-8090-E1E0626B3E1F}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="63.21875" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="16"/>
+    <col min="1" max="1" width="3.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.15">
       <c r="A1" s="15" t="s">
         <v>170</v>
       </c>
@@ -4149,7 +4199,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="17">
         <v>1</v>
       </c>
@@ -4157,7 +4207,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="17">
         <f>A2+1</f>
         <v>2</v>
@@ -4166,7 +4216,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.15">
       <c r="A4" s="17">
         <f t="shared" ref="A4:A13" si="0">A3+1</f>
         <v>3</v>
@@ -4175,7 +4225,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="17">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -4184,7 +4234,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.15">
       <c r="A6" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -4193,7 +4243,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.15">
       <c r="A7" s="17">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -4202,7 +4252,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.15">
       <c r="A8" s="17">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -4211,7 +4261,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.15">
       <c r="A9" s="17">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -4220,7 +4270,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.15">
       <c r="A10" s="17">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -4229,7 +4279,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.15">
       <c r="A11" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -4238,7 +4288,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.15">
       <c r="A12" s="17">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -4247,7 +4297,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.15">
       <c r="A13" s="17">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -4263,25 +4313,25 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB4A8877-E8DA-4C66-94BC-D151587F6D20}">
-  <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="36.44140625" customWidth="1"/>
-    <col min="3" max="3" width="14.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="59.109375" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+    <col min="2" max="2" width="36.5" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="59.1640625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="37" t="s">
-        <v>199</v>
+        <v>411</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>198</v>
       </c>
@@ -4289,117 +4339,117 @@
         <v>186</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="10">
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="A5" s="10">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C5" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
-        <v>3</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="36" t="s">
-        <v>200</v>
+        <v>412</v>
       </c>
       <c r="B11" s="36"/>
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>198</v>
       </c>
@@ -4407,114 +4457,235 @@
         <v>186</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A13" s="13">
         <v>1</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="75" x14ac:dyDescent="0.2">
       <c r="A14" s="13">
         <v>2</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" s="13">
         <v>3</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A16" s="13">
         <v>4</v>
       </c>
       <c r="B16" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="C16" s="14" t="s">
-        <v>209</v>
-      </c>
       <c r="D16" s="14" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="13">
         <v>5</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="13">
         <v>6</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A19" s="13">
         <v>7</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>215</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="36" t="s">
+        <v>413</v>
+      </c>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A24" s="13">
+        <v>1</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A25" s="13">
+        <v>2</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A26" s="13">
+        <v>3</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A27" s="13">
+        <v>4</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A28" s="13">
+        <v>5</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A29" s="13">
+        <v>6</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A30" s="13">
+        <v>7</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>429</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A22:D22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4524,153 +4695,153 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0362EF11-4C07-4F65-A6EC-3FC0EC3607B0}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="12.5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="14" max="14" width="10.21875" customWidth="1"/>
-    <col min="15" max="15" width="14.44140625" customWidth="1"/>
-    <col min="16" max="16" width="30.88671875" customWidth="1"/>
-    <col min="17" max="17" width="15.109375" customWidth="1"/>
-    <col min="18" max="18" width="12.44140625" customWidth="1"/>
+    <col min="14" max="14" width="10.1640625" customWidth="1"/>
+    <col min="15" max="15" width="14.5" customWidth="1"/>
+    <col min="16" max="16" width="30.83203125" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" customWidth="1"/>
+    <col min="18" max="18" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="77" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B1" s="31" t="s">
         <v>186</v>
       </c>
       <c r="C1" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="E1" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="F1" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="G1" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="F1" s="31" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="90" x14ac:dyDescent="0.2">
+      <c r="A2" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="B2" s="30" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="C2" s="30" t="s">
         <v>229</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="D2" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="E2" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="F2" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="G2" s="30" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.2">
+      <c r="A3" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="B3" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="G2" s="30" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="69" x14ac:dyDescent="0.3">
-      <c r="A3" s="30" t="s">
+      <c r="C3" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="D3" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="E3" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="F3" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.2">
+      <c r="A4" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>235</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="90" x14ac:dyDescent="0.2">
+      <c r="A5" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>235</v>
+      </c>
+      <c r="E5" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="D3" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="E3" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="F3" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="G3" s="30" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="30" t="s">
-        <v>240</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>242</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>243</v>
-      </c>
-      <c r="F4" s="30" t="s">
-        <v>244</v>
-      </c>
-      <c r="G4" s="30" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="30" t="s">
+      <c r="F5" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="135" x14ac:dyDescent="0.2">
+      <c r="A6" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="30" t="s">
         <v>245</v>
       </c>
-      <c r="B5" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>247</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>233</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="G5" s="30" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="138" x14ac:dyDescent="0.3">
-      <c r="A6" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>247</v>
-      </c>
       <c r="D6" s="30" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -4682,183 +4853,183 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{076153BA-5795-42F2-906B-9931FC8D5804}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="C1" s="32" t="s">
         <v>250</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="D1" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="E1" s="28" t="s">
         <v>252</v>
       </c>
-      <c r="D1" s="28" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="42" x14ac:dyDescent="0.2">
+      <c r="A2" s="29" t="s">
+        <v>257</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="42" x14ac:dyDescent="0.2">
+      <c r="A3" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>260</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="42" x14ac:dyDescent="0.2">
+      <c r="A4" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="28" x14ac:dyDescent="0.2">
+      <c r="A5" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>264</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="28" x14ac:dyDescent="0.2">
+      <c r="A6" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28" x14ac:dyDescent="0.2">
+      <c r="A7" s="29" t="s">
+        <v>267</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>268</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="28" x14ac:dyDescent="0.2">
+      <c r="A8" s="29" t="s">
+        <v>256</v>
+      </c>
+      <c r="B8" s="29" t="s">
         <v>253</v>
       </c>
-      <c r="E1" s="28" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
-        <v>259</v>
-      </c>
-      <c r="B2" s="29" t="s">
-        <v>260</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
-        <v>261</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="29" t="s">
-        <v>263</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>264</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="29" t="s">
-        <v>265</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>266</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="29" t="s">
-        <v>267</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="29" t="s">
+    <row r="9" spans="1:5" ht="28" x14ac:dyDescent="0.2">
+      <c r="A9" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B9" s="29" t="s">
         <v>270</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>255</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="D8" s="5" t="s">
+    <row r="10" spans="1:5" ht="42" x14ac:dyDescent="0.2">
+      <c r="A10" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>272</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>289</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>272</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="29" t="s">
-        <v>273</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>274</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -4872,28 +5043,28 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF75A94C-7CF8-41B9-B77E-8D74F099125C}">
   <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="8.88671875" style="1"/>
-    <col min="3" max="3" width="15.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="35.21875" style="1" customWidth="1"/>
+    <col min="1" max="2" width="8.83203125" style="1"/>
+    <col min="3" max="3" width="15.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="35.1640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:4" ht="80" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -4901,13 +5072,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="64" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -4915,41 +5086,41 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="C4" s="7" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="C4" s="7" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="A5" s="7">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:4" ht="64" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>2</v>
       </c>
@@ -4957,83 +5128,83 @@
         <v>1.2</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="A7" s="7">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
-        <v>3</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="C7" s="7" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="A8" s="7">
+        <v>3</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
-        <v>3</v>
-      </c>
-      <c r="B8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="C8" s="7" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="A9" s="7">
+        <v>3</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="C9" s="7" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
-        <v>3</v>
-      </c>
-      <c r="B9" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="C9" s="7" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="A10" s="7">
+        <v>3</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="C10" s="7" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="7">
-        <v>3</v>
-      </c>
-      <c r="B10" s="7" t="s">
+      <c r="D10" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="C10" s="7" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="A11" s="7">
+        <v>3</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7">
-        <v>3</v>
-      </c>
-      <c r="B11" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:4" ht="80" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>2</v>
       </c>
@@ -5041,111 +5212,111 @@
         <v>1.3</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="A13" s="7">
+        <v>3</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="C13" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
-        <v>3</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="64" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>4</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:4" ht="64" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>4</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="C15" s="7" t="s">
+    </row>
+    <row r="16" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="A16" s="7">
+        <v>3</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="C16" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="7">
-        <v>3</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>4</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:4" ht="48" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>4</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:4" ht="48" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>4</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:4" ht="48" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>2</v>
       </c>
@@ -5153,125 +5324,125 @@
         <v>1.4</v>
       </c>
       <c r="C20" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="A21" s="7">
+        <v>3</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="C21" s="7" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="7">
-        <v>3</v>
-      </c>
-      <c r="B21" s="7" t="s">
+      <c r="D21" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="C21" s="7" t="s">
+    </row>
+    <row r="22" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="A22" s="7">
+        <v>3</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="C22" s="7" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="7">
-        <v>3</v>
-      </c>
-      <c r="B22" s="7" t="s">
+      <c r="D22" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="C22" s="7" t="s">
+    </row>
+    <row r="23" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="A23" s="7">
+        <v>3</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="C23" s="7" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="7">
-        <v>3</v>
-      </c>
-      <c r="B23" s="7" t="s">
+      <c r="D23" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="C23" s="7" t="s">
+    </row>
+    <row r="24" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="A24" s="7">
+        <v>3</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="C24" s="7" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="7">
-        <v>3</v>
-      </c>
-      <c r="B24" s="7" t="s">
+      <c r="D24" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="C24" s="7" t="s">
+    </row>
+    <row r="25" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="A25" s="7">
+        <v>3</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="C25" s="7" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="7">
-        <v>3</v>
-      </c>
-      <c r="B25" s="7" t="s">
+      <c r="D25" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="C25" s="7" t="s">
+    </row>
+    <row r="26" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="A26" s="7">
+        <v>3</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="C26" s="7" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="7">
-        <v>3</v>
-      </c>
-      <c r="B26" s="7" t="s">
+      <c r="D26" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="C26" s="7" t="s">
+    </row>
+    <row r="27" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="A27" s="7">
+        <v>3</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="C27" s="7" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="7">
-        <v>3</v>
-      </c>
-      <c r="B27" s="7" t="s">
+      <c r="D27" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="C27" s="7" t="s">
+    </row>
+    <row r="28" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="A28" s="7">
+        <v>3</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="C28" s="7" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="7">
-        <v>3</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>392</v>
-      </c>
       <c r="D28" s="7" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="48" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
         <v>2</v>
       </c>
@@ -5279,94 +5450,94 @@
         <v>1.5</v>
       </c>
       <c r="C29" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="A30" s="7">
+        <v>3</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="C30" s="7" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="7">
-        <v>3</v>
-      </c>
-      <c r="B30" s="7" t="s">
+      <c r="D30" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="C30" s="7" t="s">
+    </row>
+    <row r="31" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="A31" s="7">
+        <v>3</v>
+      </c>
+      <c r="B31" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="C31" s="7" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="7">
-        <v>3</v>
-      </c>
-      <c r="B31" s="7" t="s">
+      <c r="D31" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="C31" s="7" t="s">
+    </row>
+    <row r="32" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A32" s="7">
+        <v>3</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="C32" s="7" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="7">
-        <v>3</v>
-      </c>
-      <c r="B32" s="7" t="s">
+      <c r="D32" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="C32" s="7" t="s">
+    </row>
+    <row r="33" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A33" s="7">
+        <v>3</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="C33" s="7" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="7">
-        <v>3</v>
-      </c>
-      <c r="B33" s="7" t="s">
+      <c r="D33" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="C33" s="7" t="s">
+    </row>
+    <row r="34" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A34" s="7">
+        <v>3</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="C34" s="7" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="7">
-        <v>3</v>
-      </c>
-      <c r="B34" s="7" t="s">
+      <c r="D34" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="C34" s="7" t="s">
+    </row>
+    <row r="35" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A35" s="7">
+        <v>3</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="C35" s="7" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="7">
-        <v>3</v>
-      </c>
-      <c r="B35" s="7" t="s">
+      <c r="D35" s="7" t="s">
         <v>410</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>412</v>
       </c>
     </row>
   </sheetData>
